--- a/artfynd/A 5162-2025 artfynd.xlsx
+++ b/artfynd/A 5162-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122606153</v>
+        <v>122607355</v>
       </c>
       <c r="B2" t="n">
-        <v>8441</v>
+        <v>79274</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599208</v>
+        <v>599190</v>
       </c>
       <c r="R2" t="n">
-        <v>6371570</v>
+        <v>6371758</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gnaggångar o kläckhål</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122607568</v>
+        <v>122607223</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>90859</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,41 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599204</v>
+        <v>599170</v>
       </c>
       <c r="R3" t="n">
-        <v>6371770</v>
+        <v>6371778</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122607223</v>
+        <v>122611546</v>
       </c>
       <c r="B4" t="n">
-        <v>90859</v>
+        <v>95009</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,41 +891,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hemängen, Hemängen, Sm</t>
+          <t>Kråkemåla, Kråkemåla, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599170</v>
+        <v>599179</v>
       </c>
       <c r="R4" t="n">
-        <v>6371778</v>
+        <v>6371843</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -961,36 +956,47 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122611553</v>
+        <v>122607568</v>
       </c>
       <c r="B5" t="n">
         <v>57399</v>
@@ -1028,24 +1034,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kråkemåla, Kråkemåla, Sm</t>
+          <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599233</v>
+        <v>599204</v>
       </c>
       <c r="R5" t="n">
-        <v>6371743</v>
+        <v>6371770</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1075,19 +1073,9 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1102,22 +1090,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122607355</v>
+        <v>122606643</v>
       </c>
       <c r="B6" t="n">
-        <v>79274</v>
+        <v>8441</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,25 +1114,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1154,13 +1142,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599190</v>
+        <v>599158</v>
       </c>
       <c r="R6" t="n">
-        <v>6371758</v>
+        <v>6371711</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,6 +1178,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1204,22 +1197,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122611546</v>
+        <v>122606737</v>
       </c>
       <c r="B7" t="n">
-        <v>95009</v>
+        <v>91233</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1232,41 +1225,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>4217</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kråkemåla, Kråkemåla, Sm</t>
+          <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599179</v>
+        <v>599180</v>
       </c>
       <c r="R7" t="n">
-        <v>6371843</v>
+        <v>6371740</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1293,50 +1282,39 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122606306</v>
+        <v>122606032</v>
       </c>
       <c r="B8" t="n">
-        <v>95009</v>
+        <v>91242</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1349,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>5420</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1373,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599154</v>
+        <v>599237</v>
       </c>
       <c r="R8" t="n">
-        <v>6371662</v>
+        <v>6371545</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,10 +1413,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122606737</v>
+        <v>122606153</v>
       </c>
       <c r="B9" t="n">
-        <v>91233</v>
+        <v>8441</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1451,21 +1429,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4217</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1475,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599180</v>
+        <v>599208</v>
       </c>
       <c r="R9" t="n">
-        <v>6371740</v>
+        <v>6371570</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,6 +1491,11 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Gnaggångar o kläckhål</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1525,22 +1508,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122606049</v>
+        <v>122611553</v>
       </c>
       <c r="B10" t="n">
-        <v>95009</v>
+        <v>57399</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,41 +1532,53 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hemängen, Hemängen, Sm</t>
+          <t>Kråkemåla, Kråkemåla, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599234</v>
+        <v>599233</v>
       </c>
       <c r="R10" t="n">
-        <v>6371534</v>
+        <v>6371743</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1610,9 +1605,19 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1639,10 +1644,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122606663</v>
+        <v>122606064</v>
       </c>
       <c r="B11" t="n">
-        <v>57399</v>
+        <v>90859</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1655,21 +1660,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599020</v>
+        <v>599237</v>
       </c>
       <c r="R11" t="n">
-        <v>6371825</v>
+        <v>6371535</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,11 +1720,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Spillkråka lokläte</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1746,10 +1746,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122607434</v>
+        <v>122606663</v>
       </c>
       <c r="B12" t="n">
-        <v>8441</v>
+        <v>57399</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1758,25 +1758,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599199</v>
+        <v>599020</v>
       </c>
       <c r="R12" t="n">
-        <v>6371748</v>
+        <v>6371825</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Gnaggångar och kläckhål</t>
+          <t>Spillkråka lokläte</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1841,19 +1841,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122606643</v>
+        <v>122607434</v>
       </c>
       <c r="B13" t="n">
         <v>8441</v>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599158</v>
+        <v>599199</v>
       </c>
       <c r="R13" t="n">
-        <v>6371711</v>
+        <v>6371748</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1960,10 +1960,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122606032</v>
+        <v>122606439</v>
       </c>
       <c r="B14" t="n">
-        <v>91242</v>
+        <v>90859</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1972,25 +1972,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5420</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2000,10 +2000,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599237</v>
+        <v>599161</v>
       </c>
       <c r="R14" t="n">
-        <v>6371545</v>
+        <v>6371656</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2062,10 +2062,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122606439</v>
+        <v>122606306</v>
       </c>
       <c r="B15" t="n">
-        <v>90859</v>
+        <v>95009</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2074,25 +2074,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599161</v>
+        <v>599154</v>
       </c>
       <c r="R15" t="n">
-        <v>6371656</v>
+        <v>6371662</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2164,10 +2164,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122606064</v>
+        <v>122606049</v>
       </c>
       <c r="B16" t="n">
-        <v>90859</v>
+        <v>95009</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2176,25 +2176,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2204,10 +2204,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599237</v>
+        <v>599234</v>
       </c>
       <c r="R16" t="n">
-        <v>6371535</v>
+        <v>6371534</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 5162-2025 artfynd.xlsx
+++ b/artfynd/A 5162-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122607355</v>
+        <v>122607434</v>
       </c>
       <c r="B2" t="n">
-        <v>79274</v>
+        <v>8441</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599190</v>
+        <v>599199</v>
       </c>
       <c r="R2" t="n">
-        <v>6371758</v>
+        <v>6371748</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122607223</v>
+        <v>122611553</v>
       </c>
       <c r="B3" t="n">
-        <v>90859</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +798,49 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hemängen, Hemängen, Sm</t>
+          <t>Kråkemåla, Kråkemåla, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599170</v>
+        <v>599233</v>
       </c>
       <c r="R3" t="n">
-        <v>6371778</v>
+        <v>6371743</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,9 +867,19 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,22 +894,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122611546</v>
+        <v>122607229</v>
       </c>
       <c r="B4" t="n">
-        <v>95009</v>
+        <v>95011</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,23 +940,19 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kråkemåla, Kråkemåla, Sm</t>
+          <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599179</v>
+        <v>599183</v>
       </c>
       <c r="R4" t="n">
-        <v>6371843</v>
+        <v>6371769</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -956,50 +979,39 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122607568</v>
+        <v>122606643</v>
       </c>
       <c r="B5" t="n">
-        <v>57399</v>
+        <v>8441</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,45 +1020,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599204</v>
+        <v>599158</v>
       </c>
       <c r="R5" t="n">
-        <v>6371770</v>
+        <v>6371711</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1076,6 +1084,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1102,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122606643</v>
+        <v>122611546</v>
       </c>
       <c r="B6" t="n">
-        <v>8441</v>
+        <v>95011</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1118,37 +1131,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hemängen, Hemängen, Sm</t>
+          <t>Kråkemåla, Kråkemåla, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599158</v>
+        <v>599179</v>
       </c>
       <c r="R6" t="n">
-        <v>6371711</v>
+        <v>6371843</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1175,14 +1192,19 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1191,18 +1213,19 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1212,7 +1235,7 @@
         <v>122606737</v>
       </c>
       <c r="B7" t="n">
-        <v>91233</v>
+        <v>91234</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1311,10 +1334,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122606032</v>
+        <v>122606153</v>
       </c>
       <c r="B8" t="n">
-        <v>91242</v>
+        <v>8441</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1350,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5420</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599237</v>
+        <v>599208</v>
       </c>
       <c r="R8" t="n">
-        <v>6371545</v>
+        <v>6371570</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,6 +1410,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gnaggångar o kläckhål</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1413,10 +1441,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122606153</v>
+        <v>122607223</v>
       </c>
       <c r="B9" t="n">
-        <v>8441</v>
+        <v>90853</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,25 +1453,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1453,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599208</v>
+        <v>599170</v>
       </c>
       <c r="R9" t="n">
-        <v>6371570</v>
+        <v>6371778</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,11 +1519,6 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Gnaggångar o kläckhål</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1508,19 +1531,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122611553</v>
+        <v>122606661</v>
       </c>
       <c r="B10" t="n">
         <v>57399</v>
@@ -1553,32 +1576,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kråkemåla, Kråkemåla, Sm</t>
+          <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599233</v>
+        <v>599020</v>
       </c>
       <c r="R10" t="n">
-        <v>6371743</v>
+        <v>6371825</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1605,19 +1616,14 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>14:30</t>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Spillkråka lokläte</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1647,7 +1653,7 @@
         <v>122606064</v>
       </c>
       <c r="B11" t="n">
-        <v>90859</v>
+        <v>90853</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1746,7 +1752,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122606663</v>
+        <v>122607568</v>
       </c>
       <c r="B12" t="n">
         <v>57399</v>
@@ -1779,20 +1785,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599020</v>
+        <v>599204</v>
       </c>
       <c r="R12" t="n">
-        <v>6371825</v>
+        <v>6371770</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1822,11 +1832,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Spillkråka lokläte</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1841,22 +1846,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122607434</v>
+        <v>122607355</v>
       </c>
       <c r="B13" t="n">
-        <v>8441</v>
+        <v>79274</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1865,25 +1870,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1893,13 +1898,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599199</v>
+        <v>599190</v>
       </c>
       <c r="R13" t="n">
-        <v>6371748</v>
+        <v>6371758</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1929,11 +1934,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1948,22 +1948,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122606439</v>
+        <v>122606306</v>
       </c>
       <c r="B14" t="n">
-        <v>90859</v>
+        <v>95011</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1972,25 +1972,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2000,10 +2000,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599161</v>
+        <v>599154</v>
       </c>
       <c r="R14" t="n">
-        <v>6371656</v>
+        <v>6371662</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2062,10 +2062,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122606306</v>
+        <v>122606439</v>
       </c>
       <c r="B15" t="n">
-        <v>95009</v>
+        <v>90853</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2074,25 +2074,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599154</v>
+        <v>599161</v>
       </c>
       <c r="R15" t="n">
-        <v>6371662</v>
+        <v>6371656</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2167,7 +2167,7 @@
         <v>122606049</v>
       </c>
       <c r="B16" t="n">
-        <v>95009</v>
+        <v>95011</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2266,10 +2266,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122607229</v>
+        <v>122606032</v>
       </c>
       <c r="B17" t="n">
-        <v>95009</v>
+        <v>91243</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2282,21 +2282,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>5420</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2306,13 +2306,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599183</v>
+        <v>599237</v>
       </c>
       <c r="R17" t="n">
-        <v>6371769</v>
+        <v>6371545</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2356,12 +2356,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 5162-2025 artfynd.xlsx
+++ b/artfynd/A 5162-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122607434</v>
+        <v>122606049</v>
       </c>
       <c r="B2" t="n">
-        <v>8441</v>
+        <v>95011</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599199</v>
+        <v>599234</v>
       </c>
       <c r="R2" t="n">
-        <v>6371748</v>
+        <v>6371534</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122611553</v>
+        <v>122606643</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>8441</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,53 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kråkemåla, Kråkemåla, Sm</t>
+          <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599233</v>
+        <v>599158</v>
       </c>
       <c r="R3" t="n">
-        <v>6371743</v>
+        <v>6371711</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,19 +850,14 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:30</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122607229</v>
+        <v>122607434</v>
       </c>
       <c r="B4" t="n">
-        <v>95011</v>
+        <v>8441</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -946,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599183</v>
+        <v>599199</v>
       </c>
       <c r="R4" t="n">
-        <v>6371769</v>
+        <v>6371748</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -982,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122606643</v>
+        <v>122606306</v>
       </c>
       <c r="B5" t="n">
-        <v>8441</v>
+        <v>95011</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,13 +1031,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599158</v>
+        <v>599154</v>
       </c>
       <c r="R5" t="n">
-        <v>6371711</v>
+        <v>6371662</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,22 +1081,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122611546</v>
+        <v>122606032</v>
       </c>
       <c r="B6" t="n">
-        <v>95011</v>
+        <v>91243</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,41 +1109,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>5420</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kråkemåla, Kråkemåla, Sm</t>
+          <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599179</v>
+        <v>599237</v>
       </c>
       <c r="R6" t="n">
-        <v>6371843</v>
+        <v>6371545</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,28 +1166,17 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1232,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122606737</v>
+        <v>122606661</v>
       </c>
       <c r="B7" t="n">
-        <v>91234</v>
+        <v>57399</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1244,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4217</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1272,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599180</v>
+        <v>599020</v>
       </c>
       <c r="R7" t="n">
-        <v>6371740</v>
+        <v>6371825</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,6 +1273,11 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Spillkråka lokläte</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1322,22 +1290,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122606153</v>
+        <v>122611553</v>
       </c>
       <c r="B8" t="n">
-        <v>8441</v>
+        <v>57399</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1346,41 +1314,53 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hemängen, Hemängen, Sm</t>
+          <t>Kråkemåla, Kråkemåla, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599208</v>
+        <v>599233</v>
       </c>
       <c r="R8" t="n">
-        <v>6371570</v>
+        <v>6371743</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,14 +1387,19 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Gnaggångar o kläckhål</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,10 +1426,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122607223</v>
+        <v>122606737</v>
       </c>
       <c r="B9" t="n">
-        <v>90853</v>
+        <v>91234</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1453,25 +1438,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>4217</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1481,10 +1466,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599170</v>
+        <v>599180</v>
       </c>
       <c r="R9" t="n">
-        <v>6371778</v>
+        <v>6371740</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1543,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122606661</v>
+        <v>122607229</v>
       </c>
       <c r="B10" t="n">
-        <v>57399</v>
+        <v>95011</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1555,25 +1540,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1583,13 +1568,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599020</v>
+        <v>599183</v>
       </c>
       <c r="R10" t="n">
-        <v>6371825</v>
+        <v>6371769</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1619,11 +1604,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Spillkråka lokläte</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,22 +1618,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122606064</v>
+        <v>122607355</v>
       </c>
       <c r="B11" t="n">
-        <v>90853</v>
+        <v>79274</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1666,21 +1646,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1690,10 +1670,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599237</v>
+        <v>599190</v>
       </c>
       <c r="R11" t="n">
-        <v>6371535</v>
+        <v>6371758</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1858,10 +1838,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122607355</v>
+        <v>122607223</v>
       </c>
       <c r="B13" t="n">
-        <v>79274</v>
+        <v>90853</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1874,21 +1854,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1898,10 +1878,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599190</v>
+        <v>599170</v>
       </c>
       <c r="R13" t="n">
-        <v>6371758</v>
+        <v>6371778</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,22 +1928,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122606306</v>
+        <v>122606153</v>
       </c>
       <c r="B14" t="n">
-        <v>95011</v>
+        <v>8441</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1976,21 +1956,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2180</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2000,10 +1980,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599154</v>
+        <v>599208</v>
       </c>
       <c r="R14" t="n">
-        <v>6371662</v>
+        <v>6371570</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2036,6 +2016,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Gnaggångar o kläckhål</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2062,7 +2047,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122606439</v>
+        <v>122606064</v>
       </c>
       <c r="B15" t="n">
         <v>90853</v>
@@ -2102,10 +2087,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599161</v>
+        <v>599237</v>
       </c>
       <c r="R15" t="n">
-        <v>6371656</v>
+        <v>6371535</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2164,10 +2149,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122606049</v>
+        <v>122606439</v>
       </c>
       <c r="B16" t="n">
-        <v>95011</v>
+        <v>90853</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2176,25 +2161,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2204,10 +2189,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599234</v>
+        <v>599161</v>
       </c>
       <c r="R16" t="n">
-        <v>6371534</v>
+        <v>6371656</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2266,10 +2251,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122606032</v>
+        <v>122611546</v>
       </c>
       <c r="B17" t="n">
-        <v>91243</v>
+        <v>95011</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2282,37 +2267,41 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5420</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hemängen, Hemängen, Sm</t>
+          <t>Kråkemåla, Kråkemåla, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599237</v>
+        <v>599179</v>
       </c>
       <c r="R17" t="n">
-        <v>6371545</v>
+        <v>6371843</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2339,17 +2328,28 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5162-2025 artfynd.xlsx
+++ b/artfynd/A 5162-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122606049</v>
+        <v>122607355</v>
       </c>
       <c r="B2" t="n">
-        <v>95011</v>
+        <v>79275</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599234</v>
+        <v>599190</v>
       </c>
       <c r="R2" t="n">
-        <v>6371534</v>
+        <v>6371758</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122606643</v>
+        <v>122606153</v>
       </c>
       <c r="B3" t="n">
         <v>8441</v>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599158</v>
+        <v>599208</v>
       </c>
       <c r="R3" t="n">
-        <v>6371711</v>
+        <v>6371570</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Gnaggångar och kläckhål</t>
+          <t>Gnaggångar o kläckhål</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122607434</v>
+        <v>122607223</v>
       </c>
       <c r="B4" t="n">
-        <v>8441</v>
+        <v>90854</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599199</v>
+        <v>599170</v>
       </c>
       <c r="R4" t="n">
-        <v>6371748</v>
+        <v>6371778</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -960,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122606306</v>
+        <v>122611546</v>
       </c>
       <c r="B5" t="n">
-        <v>95011</v>
+        <v>95012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,19 +1020,23 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hemängen, Hemängen, Sm</t>
+          <t>Kråkemåla, Kråkemåla, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599154</v>
+        <v>599179</v>
       </c>
       <c r="R5" t="n">
-        <v>6371662</v>
+        <v>6371843</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1064,17 +1063,28 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1093,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122606032</v>
+        <v>122607434</v>
       </c>
       <c r="B6" t="n">
-        <v>91243</v>
+        <v>8441</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5420</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,13 +1143,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599237</v>
+        <v>599199</v>
       </c>
       <c r="R6" t="n">
-        <v>6371545</v>
+        <v>6371748</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1169,6 +1179,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,22 +1198,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122606661</v>
+        <v>122606049</v>
       </c>
       <c r="B7" t="n">
-        <v>57399</v>
+        <v>95012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1222,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599020</v>
+        <v>599234</v>
       </c>
       <c r="R7" t="n">
-        <v>6371825</v>
+        <v>6371534</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,11 +1286,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Spillkråka lokläte</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122611553</v>
+        <v>122606661</v>
       </c>
       <c r="B8" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1335,32 +1345,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kråkemåla, Kråkemåla, Sm</t>
+          <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599233</v>
+        <v>599020</v>
       </c>
       <c r="R8" t="n">
-        <v>6371743</v>
+        <v>6371825</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1387,19 +1385,14 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:30</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Spillkråka lokläte</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,7 +1422,7 @@
         <v>122606737</v>
       </c>
       <c r="B9" t="n">
-        <v>91234</v>
+        <v>91235</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1528,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122607229</v>
+        <v>122611553</v>
       </c>
       <c r="B10" t="n">
-        <v>95011</v>
+        <v>57400</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,41 +1533,53 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hemängen, Hemängen, Sm</t>
+          <t>Kråkemåla, Kråkemåla, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599183</v>
+        <v>599233</v>
       </c>
       <c r="R10" t="n">
-        <v>6371769</v>
+        <v>6371743</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1601,9 +1606,19 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,22 +1633,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122607355</v>
+        <v>122606064</v>
       </c>
       <c r="B11" t="n">
-        <v>79274</v>
+        <v>90854</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,21 +1661,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1670,10 +1685,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599190</v>
+        <v>599237</v>
       </c>
       <c r="R11" t="n">
-        <v>6371758</v>
+        <v>6371535</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1732,10 +1747,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122607568</v>
+        <v>122606643</v>
       </c>
       <c r="B12" t="n">
-        <v>57399</v>
+        <v>8441</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1744,45 +1759,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599204</v>
+        <v>599158</v>
       </c>
       <c r="R12" t="n">
-        <v>6371770</v>
+        <v>6371711</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1812,6 +1823,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1838,10 +1854,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122607223</v>
+        <v>122607229</v>
       </c>
       <c r="B13" t="n">
-        <v>90853</v>
+        <v>95012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1850,25 +1866,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1878,13 +1894,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599170</v>
+        <v>599183</v>
       </c>
       <c r="R13" t="n">
-        <v>6371778</v>
+        <v>6371769</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1940,10 +1956,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122606153</v>
+        <v>122606306</v>
       </c>
       <c r="B14" t="n">
-        <v>8441</v>
+        <v>95012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1956,21 +1972,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1980,10 +1996,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599208</v>
+        <v>599154</v>
       </c>
       <c r="R14" t="n">
-        <v>6371570</v>
+        <v>6371662</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2016,11 +2032,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Gnaggångar o kläckhål</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2047,10 +2058,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122606064</v>
+        <v>122606439</v>
       </c>
       <c r="B15" t="n">
-        <v>90853</v>
+        <v>90854</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2087,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599237</v>
+        <v>599161</v>
       </c>
       <c r="R15" t="n">
-        <v>6371535</v>
+        <v>6371656</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2149,10 +2160,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122606439</v>
+        <v>122606032</v>
       </c>
       <c r="B16" t="n">
-        <v>90853</v>
+        <v>91244</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2161,25 +2172,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2189,10 +2200,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599161</v>
+        <v>599237</v>
       </c>
       <c r="R16" t="n">
-        <v>6371656</v>
+        <v>6371545</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2251,10 +2262,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122611546</v>
+        <v>122607568</v>
       </c>
       <c r="B17" t="n">
-        <v>95011</v>
+        <v>57400</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2263,42 +2274,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kråkemåla, Kråkemåla, Sm</t>
+          <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599179</v>
+        <v>599204</v>
       </c>
       <c r="R17" t="n">
-        <v>6371843</v>
+        <v>6371770</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2328,40 +2339,29 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 5162-2025 artfynd.xlsx
+++ b/artfynd/A 5162-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122607355</v>
+        <v>122606153</v>
       </c>
       <c r="B2" t="n">
-        <v>79275</v>
+        <v>8441</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599190</v>
+        <v>599208</v>
       </c>
       <c r="R2" t="n">
-        <v>6371758</v>
+        <v>6371570</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Gnaggångar o kläckhål</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122606153</v>
+        <v>122607355</v>
       </c>
       <c r="B3" t="n">
-        <v>8441</v>
+        <v>79275</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599208</v>
+        <v>599190</v>
       </c>
       <c r="R3" t="n">
-        <v>6371570</v>
+        <v>6371758</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gnaggångar o kläckhål</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 5162-2025 artfynd.xlsx
+++ b/artfynd/A 5162-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122611546</v>
+        <v>122607568</v>
       </c>
       <c r="B3" t="n">
-        <v>95118</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,42 +794,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kråkemåla, Kråkemåla, Sm</t>
+          <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599179</v>
+        <v>599204</v>
       </c>
       <c r="R3" t="n">
-        <v>6371843</v>
+        <v>6371770</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -859,50 +859,39 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122607568</v>
+        <v>122611546</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>95118</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,42 +900,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hemängen, Hemängen, Sm</t>
+          <t>Kråkemåla, Kråkemåla, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599204</v>
+        <v>599179</v>
       </c>
       <c r="R4" t="n">
-        <v>6371770</v>
+        <v>6371843</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -976,29 +965,40 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1525,10 +1525,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122611553</v>
+        <v>122606643</v>
       </c>
       <c r="B10" t="n">
-        <v>57494</v>
+        <v>8441</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,53 +1537,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kråkemåla, Kråkemåla, Sm</t>
+          <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599233</v>
+        <v>599158</v>
       </c>
       <c r="R10" t="n">
-        <v>6371743</v>
+        <v>6371711</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1610,19 +1598,14 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>14:30</t>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1637,12 +1620,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1751,10 +1734,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122606643</v>
+        <v>122611553</v>
       </c>
       <c r="B12" t="n">
-        <v>8441</v>
+        <v>57494</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1763,41 +1746,53 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hemängen, Hemängen, Sm</t>
+          <t>Kråkemåla, Kråkemåla, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599158</v>
+        <v>599233</v>
       </c>
       <c r="R12" t="n">
-        <v>6371711</v>
+        <v>6371743</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1824,14 +1819,19 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1846,12 +1846,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 5162-2025 artfynd.xlsx
+++ b/artfynd/A 5162-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122607568</v>
+        <v>122611546</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>95118</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,42 +794,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hemängen, Hemängen, Sm</t>
+          <t>Kråkemåla, Kråkemåla, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599204</v>
+        <v>599179</v>
       </c>
       <c r="R3" t="n">
-        <v>6371770</v>
+        <v>6371843</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -859,39 +859,50 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122611546</v>
+        <v>122607568</v>
       </c>
       <c r="B4" t="n">
-        <v>95118</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,42 +911,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kråkemåla, Kråkemåla, Sm</t>
+          <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599179</v>
+        <v>599204</v>
       </c>
       <c r="R4" t="n">
-        <v>6371843</v>
+        <v>6371770</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -965,40 +976,29 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1858,10 +1858,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122606049</v>
+        <v>122606064</v>
       </c>
       <c r="B13" t="n">
-        <v>95118</v>
+        <v>90960</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1870,25 +1870,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1898,10 +1898,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599234</v>
+        <v>599237</v>
       </c>
       <c r="R13" t="n">
-        <v>6371534</v>
+        <v>6371535</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1960,7 +1960,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122606064</v>
+        <v>122607223</v>
       </c>
       <c r="B14" t="n">
         <v>90960</v>
@@ -2000,10 +2000,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599237</v>
+        <v>599170</v>
       </c>
       <c r="R14" t="n">
-        <v>6371535</v>
+        <v>6371778</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2050,22 +2050,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122607223</v>
+        <v>122606049</v>
       </c>
       <c r="B15" t="n">
-        <v>90960</v>
+        <v>95118</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2074,25 +2074,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599170</v>
+        <v>599234</v>
       </c>
       <c r="R15" t="n">
-        <v>6371778</v>
+        <v>6371534</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2152,12 +2152,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122793965</v>
+        <v>122793956</v>
       </c>
       <c r="B18" t="n">
-        <v>79380</v>
+        <v>95126</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2380,30 +2380,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2411,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599017</v>
+        <v>599063</v>
       </c>
       <c r="R18" t="n">
-        <v>6371791</v>
+        <v>6371790</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2484,10 +2485,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122793956</v>
+        <v>122793941</v>
       </c>
       <c r="B19" t="n">
-        <v>95118</v>
+        <v>8441</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2500,27 +2501,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2528,10 +2530,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599063</v>
+        <v>599230</v>
       </c>
       <c r="R19" t="n">
-        <v>6371790</v>
+        <v>6371555</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2601,10 +2603,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122793949</v>
+        <v>122793965</v>
       </c>
       <c r="B20" t="n">
-        <v>95118</v>
+        <v>79384</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2613,31 +2615,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2645,10 +2646,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599171</v>
+        <v>599017</v>
       </c>
       <c r="R20" t="n">
-        <v>6371603</v>
+        <v>6371791</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2718,10 +2719,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122793941</v>
+        <v>122793949</v>
       </c>
       <c r="B21" t="n">
-        <v>8441</v>
+        <v>95126</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2734,28 +2735,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599230</v>
+        <v>599171</v>
       </c>
       <c r="R21" t="n">
-        <v>6371555</v>
+        <v>6371603</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 5162-2025 artfynd.xlsx
+++ b/artfynd/A 5162-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122606661</v>
+        <v>122607434</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>8441</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599020</v>
+        <v>599199</v>
       </c>
       <c r="R2" t="n">
-        <v>6371825</v>
+        <v>6371748</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Spillkråka lokläte</t>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122611546</v>
+        <v>122607568</v>
       </c>
       <c r="B3" t="n">
-        <v>95118</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,42 +794,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kråkemåla, Kråkemåla, Sm</t>
+          <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599179</v>
+        <v>599204</v>
       </c>
       <c r="R3" t="n">
-        <v>6371843</v>
+        <v>6371770</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -859,50 +859,39 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122607568</v>
+        <v>122606643</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>8441</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,45 +900,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599204</v>
+        <v>599158</v>
       </c>
       <c r="R4" t="n">
-        <v>6371770</v>
+        <v>6371711</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,6 +964,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122607229</v>
+        <v>122606439</v>
       </c>
       <c r="B5" t="n">
-        <v>95118</v>
+        <v>90964</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,25 +1007,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1045,13 +1035,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599183</v>
+        <v>599161</v>
       </c>
       <c r="R5" t="n">
-        <v>6371769</v>
+        <v>6371656</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,22 +1085,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122606439</v>
+        <v>122606737</v>
       </c>
       <c r="B6" t="n">
-        <v>90960</v>
+        <v>91345</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,25 +1109,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>4217</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1147,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599161</v>
+        <v>599180</v>
       </c>
       <c r="R6" t="n">
-        <v>6371656</v>
+        <v>6371740</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,22 +1187,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122606306</v>
+        <v>122611546</v>
       </c>
       <c r="B7" t="n">
-        <v>95118</v>
+        <v>95126</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,19 +1233,23 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hemängen, Hemängen, Sm</t>
+          <t>Kråkemåla, Kråkemåla, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599154</v>
+        <v>599179</v>
       </c>
       <c r="R7" t="n">
-        <v>6371662</v>
+        <v>6371843</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1282,17 +1276,28 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1418,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122607434</v>
+        <v>122606663</v>
       </c>
       <c r="B9" t="n">
-        <v>8441</v>
+        <v>57494</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,25 +1435,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1458,13 +1463,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599199</v>
+        <v>599020</v>
       </c>
       <c r="R9" t="n">
-        <v>6371748</v>
+        <v>6371825</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1498,7 +1503,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Gnaggångar och kläckhål</t>
+          <t>Spillkråka lokläte</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1513,22 +1518,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122606643</v>
+        <v>122611553</v>
       </c>
       <c r="B10" t="n">
-        <v>8441</v>
+        <v>57494</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,41 +1542,53 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hemängen, Hemängen, Sm</t>
+          <t>Kråkemåla, Kråkemåla, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599158</v>
+        <v>599233</v>
       </c>
       <c r="R10" t="n">
-        <v>6371711</v>
+        <v>6371743</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1598,14 +1615,19 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1620,22 +1642,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122607355</v>
+        <v>122606064</v>
       </c>
       <c r="B11" t="n">
-        <v>79380</v>
+        <v>90964</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1648,21 +1670,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1672,10 +1694,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599190</v>
+        <v>599237</v>
       </c>
       <c r="R11" t="n">
-        <v>6371758</v>
+        <v>6371535</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,10 +1756,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122611553</v>
+        <v>122606032</v>
       </c>
       <c r="B12" t="n">
-        <v>57494</v>
+        <v>91354</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1746,53 +1768,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>5420</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kråkemåla, Kråkemåla, Sm</t>
+          <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599233</v>
+        <v>599237</v>
       </c>
       <c r="R12" t="n">
-        <v>6371743</v>
+        <v>6371545</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1819,19 +1829,9 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1858,10 +1858,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122606064</v>
+        <v>122606049</v>
       </c>
       <c r="B13" t="n">
-        <v>90960</v>
+        <v>95126</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1870,25 +1870,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1898,10 +1898,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599237</v>
+        <v>599234</v>
       </c>
       <c r="R13" t="n">
-        <v>6371535</v>
+        <v>6371534</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1960,10 +1960,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122607223</v>
+        <v>122607229</v>
       </c>
       <c r="B14" t="n">
-        <v>90960</v>
+        <v>95126</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1972,25 +1972,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2000,13 +2000,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599170</v>
+        <v>599183</v>
       </c>
       <c r="R14" t="n">
-        <v>6371778</v>
+        <v>6371769</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2062,10 +2062,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122606049</v>
+        <v>122607223</v>
       </c>
       <c r="B15" t="n">
-        <v>95118</v>
+        <v>90964</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2074,25 +2074,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599234</v>
+        <v>599170</v>
       </c>
       <c r="R15" t="n">
-        <v>6371534</v>
+        <v>6371778</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2152,22 +2152,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122606737</v>
+        <v>122606306</v>
       </c>
       <c r="B16" t="n">
-        <v>91341</v>
+        <v>95126</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2180,21 +2180,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4217</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2204,10 +2204,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599180</v>
+        <v>599154</v>
       </c>
       <c r="R16" t="n">
-        <v>6371740</v>
+        <v>6371662</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2254,22 +2254,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122606032</v>
+        <v>122607355</v>
       </c>
       <c r="B17" t="n">
-        <v>91350</v>
+        <v>79384</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2278,25 +2278,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5420</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2306,10 +2306,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599237</v>
+        <v>599190</v>
       </c>
       <c r="R17" t="n">
-        <v>6371545</v>
+        <v>6371758</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 5162-2025 artfynd.xlsx
+++ b/artfynd/A 5162-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122607434</v>
+        <v>122607223</v>
       </c>
       <c r="B2" t="n">
-        <v>8441</v>
+        <v>90964</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599199</v>
+        <v>599170</v>
       </c>
       <c r="R2" t="n">
-        <v>6371748</v>
+        <v>6371778</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122607568</v>
+        <v>122606643</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>8441</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,45 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599204</v>
+        <v>599158</v>
       </c>
       <c r="R3" t="n">
-        <v>6371770</v>
+        <v>6371711</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122606643</v>
+        <v>122606064</v>
       </c>
       <c r="B4" t="n">
-        <v>8441</v>
+        <v>90964</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599158</v>
+        <v>599237</v>
       </c>
       <c r="R4" t="n">
-        <v>6371711</v>
+        <v>6371535</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -983,22 +974,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122606439</v>
+        <v>122606661</v>
       </c>
       <c r="B5" t="n">
-        <v>90964</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1035,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599161</v>
+        <v>599020</v>
       </c>
       <c r="R5" t="n">
-        <v>6371656</v>
+        <v>6371825</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spillkråka lokläte</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122606737</v>
+        <v>122607355</v>
       </c>
       <c r="B6" t="n">
-        <v>91345</v>
+        <v>79384</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4217</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1137,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599180</v>
+        <v>599190</v>
       </c>
       <c r="R6" t="n">
-        <v>6371740</v>
+        <v>6371758</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,22 +1183,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122611546</v>
+        <v>122607434</v>
       </c>
       <c r="B7" t="n">
-        <v>95126</v>
+        <v>8441</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,41 +1211,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kråkemåla, Kråkemåla, Sm</t>
+          <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599179</v>
+        <v>599199</v>
       </c>
       <c r="R7" t="n">
-        <v>6371843</v>
+        <v>6371748</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1276,19 +1268,14 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:30</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,29 +1284,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122606153</v>
+        <v>122607229</v>
       </c>
       <c r="B8" t="n">
-        <v>8441</v>
+        <v>95126</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,13 +1342,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599208</v>
+        <v>599183</v>
       </c>
       <c r="R8" t="n">
-        <v>6371570</v>
+        <v>6371769</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1392,11 +1378,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Gnaggångar o kläckhål</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1411,22 +1392,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122606663</v>
+        <v>122606032</v>
       </c>
       <c r="B9" t="n">
-        <v>57494</v>
+        <v>91354</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,25 +1416,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5420</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1463,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599020</v>
+        <v>599237</v>
       </c>
       <c r="R9" t="n">
-        <v>6371825</v>
+        <v>6371545</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,11 +1480,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Spillkråka lokläte</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1530,7 +1506,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122611553</v>
+        <v>122607568</v>
       </c>
       <c r="B10" t="n">
         <v>57494</v>
@@ -1568,24 +1544,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kråkemåla, Kråkemåla, Sm</t>
+          <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599233</v>
+        <v>599204</v>
       </c>
       <c r="R10" t="n">
-        <v>6371743</v>
+        <v>6371770</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1615,19 +1583,9 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>14:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1642,22 +1600,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122606064</v>
+        <v>122611546</v>
       </c>
       <c r="B11" t="n">
-        <v>90964</v>
+        <v>95126</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1666,41 +1624,45 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hemängen, Hemängen, Sm</t>
+          <t>Kråkemåla, Kråkemåla, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599237</v>
+        <v>599179</v>
       </c>
       <c r="R11" t="n">
-        <v>6371535</v>
+        <v>6371843</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1727,17 +1689,28 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1756,10 +1729,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122606032</v>
+        <v>122606439</v>
       </c>
       <c r="B12" t="n">
-        <v>91354</v>
+        <v>90964</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1768,25 +1741,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5420</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1796,10 +1769,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599237</v>
+        <v>599161</v>
       </c>
       <c r="R12" t="n">
-        <v>6371545</v>
+        <v>6371656</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1858,10 +1831,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122606049</v>
+        <v>122611553</v>
       </c>
       <c r="B13" t="n">
-        <v>95126</v>
+        <v>57494</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1870,41 +1843,53 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hemängen, Hemängen, Sm</t>
+          <t>Kråkemåla, Kråkemåla, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599234</v>
+        <v>599233</v>
       </c>
       <c r="R13" t="n">
-        <v>6371534</v>
+        <v>6371743</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1931,9 +1916,19 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1960,10 +1955,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122607229</v>
+        <v>122606737</v>
       </c>
       <c r="B14" t="n">
-        <v>95126</v>
+        <v>91345</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1976,21 +1971,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2180</v>
+        <v>4217</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2000,13 +1995,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599183</v>
+        <v>599180</v>
       </c>
       <c r="R14" t="n">
-        <v>6371769</v>
+        <v>6371740</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2062,10 +2057,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122607223</v>
+        <v>122606306</v>
       </c>
       <c r="B15" t="n">
-        <v>90964</v>
+        <v>95126</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2074,25 +2069,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2102,10 +2097,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599170</v>
+        <v>599154</v>
       </c>
       <c r="R15" t="n">
-        <v>6371778</v>
+        <v>6371662</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2152,19 +2147,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122606306</v>
+        <v>122606049</v>
       </c>
       <c r="B16" t="n">
         <v>95126</v>
@@ -2204,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599154</v>
+        <v>599234</v>
       </c>
       <c r="R16" t="n">
-        <v>6371662</v>
+        <v>6371534</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2266,10 +2261,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122607355</v>
+        <v>122606153</v>
       </c>
       <c r="B17" t="n">
-        <v>79384</v>
+        <v>8441</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2278,25 +2273,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2306,10 +2301,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599190</v>
+        <v>599208</v>
       </c>
       <c r="R17" t="n">
-        <v>6371758</v>
+        <v>6371570</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2342,6 +2337,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Gnaggångar o kläckhål</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2368,7 +2368,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122793956</v>
+        <v>122793949</v>
       </c>
       <c r="B18" t="n">
         <v>95126</v>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599063</v>
+        <v>599171</v>
       </c>
       <c r="R18" t="n">
-        <v>6371790</v>
+        <v>6371603</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2485,10 +2485,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122793941</v>
+        <v>122793965</v>
       </c>
       <c r="B19" t="n">
-        <v>8441</v>
+        <v>79384</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2497,32 +2497,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2530,10 +2528,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599230</v>
+        <v>599017</v>
       </c>
       <c r="R19" t="n">
-        <v>6371555</v>
+        <v>6371791</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2603,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122793965</v>
+        <v>122793941</v>
       </c>
       <c r="B20" t="n">
-        <v>79384</v>
+        <v>8441</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2615,30 +2613,32 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599017</v>
+        <v>599230</v>
       </c>
       <c r="R20" t="n">
-        <v>6371791</v>
+        <v>6371555</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2719,7 +2719,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122793949</v>
+        <v>122793956</v>
       </c>
       <c r="B21" t="n">
         <v>95126</v>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599171</v>
+        <v>599063</v>
       </c>
       <c r="R21" t="n">
-        <v>6371603</v>
+        <v>6371790</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 5162-2025 artfynd.xlsx
+++ b/artfynd/A 5162-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122607223</v>
+        <v>122606643</v>
       </c>
       <c r="B2" t="n">
-        <v>90964</v>
+        <v>8441</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599170</v>
+        <v>599158</v>
       </c>
       <c r="R2" t="n">
-        <v>6371778</v>
+        <v>6371711</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122606643</v>
+        <v>122606439</v>
       </c>
       <c r="B3" t="n">
-        <v>8441</v>
+        <v>90964</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599158</v>
+        <v>599161</v>
       </c>
       <c r="R3" t="n">
-        <v>6371711</v>
+        <v>6371656</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122606064</v>
+        <v>122606049</v>
       </c>
       <c r="B4" t="n">
-        <v>90964</v>
+        <v>95128</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599237</v>
+        <v>599234</v>
       </c>
       <c r="R4" t="n">
-        <v>6371535</v>
+        <v>6371534</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122606661</v>
+        <v>122606153</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>8441</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599020</v>
+        <v>599208</v>
       </c>
       <c r="R5" t="n">
-        <v>6371825</v>
+        <v>6371570</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Spillkråka lokläte</t>
+          <t>Gnaggångar o kläckhål</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122607355</v>
+        <v>122606032</v>
       </c>
       <c r="B6" t="n">
-        <v>79384</v>
+        <v>91354</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>5420</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599190</v>
+        <v>599237</v>
       </c>
       <c r="R6" t="n">
-        <v>6371758</v>
+        <v>6371545</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122607434</v>
+        <v>122606306</v>
       </c>
       <c r="B7" t="n">
-        <v>8441</v>
+        <v>95128</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,13 +1235,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599199</v>
+        <v>599154</v>
       </c>
       <c r="R7" t="n">
-        <v>6371748</v>
+        <v>6371662</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1271,11 +1271,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1290,22 +1285,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122607229</v>
+        <v>122607223</v>
       </c>
       <c r="B8" t="n">
-        <v>95126</v>
+        <v>90964</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1314,25 +1309,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,13 +1337,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599183</v>
+        <v>599170</v>
       </c>
       <c r="R8" t="n">
-        <v>6371769</v>
+        <v>6371778</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1404,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122606032</v>
+        <v>122606663</v>
       </c>
       <c r="B9" t="n">
-        <v>91354</v>
+        <v>57494</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1416,25 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5420</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599237</v>
+        <v>599020</v>
       </c>
       <c r="R9" t="n">
-        <v>6371545</v>
+        <v>6371825</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,6 +1475,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Spillkråka lokläte</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122607568</v>
+        <v>122607355</v>
       </c>
       <c r="B10" t="n">
-        <v>57494</v>
+        <v>79384</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,41 +1522,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599204</v>
+        <v>599190</v>
       </c>
       <c r="R10" t="n">
-        <v>6371770</v>
+        <v>6371758</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1600,22 +1596,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122611546</v>
+        <v>122611553</v>
       </c>
       <c r="B11" t="n">
-        <v>95126</v>
+        <v>57494</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,31 +1620,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1656,10 +1660,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599179</v>
+        <v>599233</v>
       </c>
       <c r="R11" t="n">
-        <v>6371843</v>
+        <v>6371743</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1710,7 +1714,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1729,10 +1732,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122606439</v>
+        <v>122607434</v>
       </c>
       <c r="B12" t="n">
-        <v>90964</v>
+        <v>8441</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1741,25 +1744,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1769,13 +1772,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599161</v>
+        <v>599199</v>
       </c>
       <c r="R12" t="n">
-        <v>6371656</v>
+        <v>6371748</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1805,6 +1808,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1819,22 +1827,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122611553</v>
+        <v>122607229</v>
       </c>
       <c r="B13" t="n">
-        <v>57494</v>
+        <v>95128</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1843,53 +1851,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kråkemåla, Kråkemåla, Sm</t>
+          <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599233</v>
+        <v>599183</v>
       </c>
       <c r="R13" t="n">
-        <v>6371743</v>
+        <v>6371769</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1916,19 +1912,9 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1943,22 +1929,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122606737</v>
+        <v>122606064</v>
       </c>
       <c r="B14" t="n">
-        <v>91345</v>
+        <v>90964</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1967,25 +1953,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4217</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1995,10 +1981,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599180</v>
+        <v>599237</v>
       </c>
       <c r="R14" t="n">
-        <v>6371740</v>
+        <v>6371535</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2045,22 +2031,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122606306</v>
+        <v>122607568</v>
       </c>
       <c r="B15" t="n">
-        <v>95126</v>
+        <v>57494</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,41 +2055,45 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599154</v>
+        <v>599204</v>
       </c>
       <c r="R15" t="n">
-        <v>6371662</v>
+        <v>6371770</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2147,22 +2137,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122606049</v>
+        <v>122606737</v>
       </c>
       <c r="B16" t="n">
-        <v>95126</v>
+        <v>91345</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,21 +2165,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>4217</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2199,10 +2189,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599234</v>
+        <v>599180</v>
       </c>
       <c r="R16" t="n">
-        <v>6371534</v>
+        <v>6371740</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2249,22 +2239,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122606153</v>
+        <v>122611546</v>
       </c>
       <c r="B17" t="n">
-        <v>8441</v>
+        <v>95128</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2277,37 +2267,41 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hemängen, Hemängen, Sm</t>
+          <t>Kråkemåla, Kråkemåla, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599208</v>
+        <v>599179</v>
       </c>
       <c r="R17" t="n">
-        <v>6371570</v>
+        <v>6371843</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2334,14 +2328,19 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Gnaggångar o kläckhål</t>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2350,6 +2349,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2371,7 +2371,7 @@
         <v>122793949</v>
       </c>
       <c r="B18" t="n">
-        <v>95126</v>
+        <v>95128</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2601,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122793941</v>
+        <v>122793956</v>
       </c>
       <c r="B20" t="n">
-        <v>8441</v>
+        <v>95128</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2617,28 +2617,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2646,10 +2645,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599230</v>
+        <v>599063</v>
       </c>
       <c r="R20" t="n">
-        <v>6371555</v>
+        <v>6371790</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2719,10 +2718,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122793956</v>
+        <v>122793941</v>
       </c>
       <c r="B21" t="n">
-        <v>95126</v>
+        <v>8441</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2735,27 +2734,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2180</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599063</v>
+        <v>599230</v>
       </c>
       <c r="R21" t="n">
-        <v>6371790</v>
+        <v>6371555</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 5162-2025 artfynd.xlsx
+++ b/artfynd/A 5162-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122606643</v>
+        <v>122607434</v>
       </c>
       <c r="B2" t="n">
         <v>8441</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599158</v>
+        <v>599199</v>
       </c>
       <c r="R2" t="n">
-        <v>6371711</v>
+        <v>6371748</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122606439</v>
+        <v>122607568</v>
       </c>
       <c r="B3" t="n">
-        <v>90964</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,37 +798,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599161</v>
+        <v>599204</v>
       </c>
       <c r="R3" t="n">
-        <v>6371656</v>
+        <v>6371770</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,19 +876,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122606049</v>
+        <v>122606306</v>
       </c>
       <c r="B4" t="n">
         <v>95128</v>
@@ -924,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599234</v>
+        <v>599154</v>
       </c>
       <c r="R4" t="n">
-        <v>6371534</v>
+        <v>6371662</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122606153</v>
+        <v>122607355</v>
       </c>
       <c r="B5" t="n">
-        <v>8441</v>
+        <v>79384</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +1002,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599208</v>
+        <v>599190</v>
       </c>
       <c r="R5" t="n">
-        <v>6371570</v>
+        <v>6371758</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1066,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Gnaggångar o kläckhål</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122606032</v>
+        <v>122606153</v>
       </c>
       <c r="B6" t="n">
-        <v>91354</v>
+        <v>8441</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1108,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5420</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599237</v>
+        <v>599208</v>
       </c>
       <c r="R6" t="n">
-        <v>6371545</v>
+        <v>6371570</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1168,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gnaggångar o kläckhål</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122606306</v>
+        <v>122606663</v>
       </c>
       <c r="B7" t="n">
-        <v>95128</v>
+        <v>57494</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1211,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599154</v>
+        <v>599020</v>
       </c>
       <c r="R7" t="n">
-        <v>6371662</v>
+        <v>6371825</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,6 +1275,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Spillkråka lokläte</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,10 +1306,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122607223</v>
+        <v>122606643</v>
       </c>
       <c r="B8" t="n">
-        <v>90964</v>
+        <v>8441</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,25 +1318,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,13 +1346,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599170</v>
+        <v>599158</v>
       </c>
       <c r="R8" t="n">
-        <v>6371778</v>
+        <v>6371711</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1373,6 +1382,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,10 +1413,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122606663</v>
+        <v>122606064</v>
       </c>
       <c r="B9" t="n">
-        <v>57494</v>
+        <v>90964</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,21 +1429,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599020</v>
+        <v>599237</v>
       </c>
       <c r="R9" t="n">
-        <v>6371825</v>
+        <v>6371535</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,11 +1489,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Spillkråka lokläte</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122607355</v>
+        <v>122607229</v>
       </c>
       <c r="B10" t="n">
-        <v>79384</v>
+        <v>95128</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1518,25 +1527,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,13 +1555,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599190</v>
+        <v>599183</v>
       </c>
       <c r="R10" t="n">
-        <v>6371758</v>
+        <v>6371769</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1596,22 +1605,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122611553</v>
+        <v>122606439</v>
       </c>
       <c r="B11" t="n">
-        <v>57494</v>
+        <v>90964</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,49 +1633,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kråkemåla, Kråkemåla, Sm</t>
+          <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599233</v>
+        <v>599161</v>
       </c>
       <c r="R11" t="n">
-        <v>6371743</v>
+        <v>6371656</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1693,19 +1690,9 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1732,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122607434</v>
+        <v>122606032</v>
       </c>
       <c r="B12" t="n">
-        <v>8441</v>
+        <v>91354</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1748,21 +1735,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>5420</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1772,13 +1759,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599199</v>
+        <v>599237</v>
       </c>
       <c r="R12" t="n">
-        <v>6371748</v>
+        <v>6371545</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1808,11 +1795,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1827,19 +1809,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122607229</v>
+        <v>122611546</v>
       </c>
       <c r="B13" t="n">
         <v>95128</v>
@@ -1873,19 +1855,23 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hemängen, Hemängen, Sm</t>
+          <t>Kråkemåla, Kråkemåla, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599183</v>
+        <v>599179</v>
       </c>
       <c r="R13" t="n">
-        <v>6371769</v>
+        <v>6371843</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1912,36 +1898,47 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122606064</v>
+        <v>122607223</v>
       </c>
       <c r="B14" t="n">
         <v>90964</v>
@@ -1981,10 +1978,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599237</v>
+        <v>599170</v>
       </c>
       <c r="R14" t="n">
-        <v>6371535</v>
+        <v>6371778</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2031,22 +2028,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122607568</v>
+        <v>122606737</v>
       </c>
       <c r="B15" t="n">
-        <v>57494</v>
+        <v>91345</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2055,45 +2052,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>4217</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599204</v>
+        <v>599180</v>
       </c>
       <c r="R15" t="n">
-        <v>6371770</v>
+        <v>6371740</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2149,10 +2142,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122606737</v>
+        <v>122606049</v>
       </c>
       <c r="B16" t="n">
-        <v>91345</v>
+        <v>95128</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2165,21 +2158,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4217</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2189,10 +2182,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599180</v>
+        <v>599234</v>
       </c>
       <c r="R16" t="n">
-        <v>6371740</v>
+        <v>6371534</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2239,22 +2232,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122611546</v>
+        <v>122611553</v>
       </c>
       <c r="B17" t="n">
-        <v>95128</v>
+        <v>57494</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2263,31 +2256,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2295,10 +2296,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599179</v>
+        <v>599233</v>
       </c>
       <c r="R17" t="n">
-        <v>6371843</v>
+        <v>6371743</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2349,7 +2350,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2368,7 +2368,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122793949</v>
+        <v>122793956</v>
       </c>
       <c r="B18" t="n">
         <v>95128</v>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599171</v>
+        <v>599063</v>
       </c>
       <c r="R18" t="n">
-        <v>6371603</v>
+        <v>6371790</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2485,10 +2485,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122793965</v>
+        <v>122793949</v>
       </c>
       <c r="B19" t="n">
-        <v>79384</v>
+        <v>95128</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2497,30 +2497,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2528,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599017</v>
+        <v>599171</v>
       </c>
       <c r="R19" t="n">
-        <v>6371791</v>
+        <v>6371603</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2601,10 +2602,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122793956</v>
+        <v>122793941</v>
       </c>
       <c r="B20" t="n">
-        <v>95128</v>
+        <v>8441</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2617,27 +2618,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2180</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2645,10 +2647,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599063</v>
+        <v>599230</v>
       </c>
       <c r="R20" t="n">
-        <v>6371790</v>
+        <v>6371555</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2718,10 +2720,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122793941</v>
+        <v>122793965</v>
       </c>
       <c r="B21" t="n">
-        <v>8441</v>
+        <v>79384</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2730,32 +2732,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599230</v>
+        <v>599017</v>
       </c>
       <c r="R21" t="n">
-        <v>6371555</v>
+        <v>6371791</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 5162-2025 artfynd.xlsx
+++ b/artfynd/A 5162-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122607434</v>
+        <v>122606032</v>
       </c>
       <c r="B2" t="n">
-        <v>8441</v>
+        <v>91362</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599199</v>
+        <v>599237</v>
       </c>
       <c r="R2" t="n">
-        <v>6371748</v>
+        <v>6371545</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122607568</v>
+        <v>122611546</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>95136</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,42 +789,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hemängen, Hemängen, Sm</t>
+          <t>Kråkemåla, Kråkemåla, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599204</v>
+        <v>599179</v>
       </c>
       <c r="R3" t="n">
-        <v>6371770</v>
+        <v>6371843</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -859,39 +854,50 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122606306</v>
+        <v>122606643</v>
       </c>
       <c r="B4" t="n">
-        <v>95128</v>
+        <v>8441</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,13 +934,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599154</v>
+        <v>599158</v>
       </c>
       <c r="R4" t="n">
-        <v>6371662</v>
+        <v>6371711</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,6 +970,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -978,22 +989,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122607355</v>
+        <v>122606737</v>
       </c>
       <c r="B5" t="n">
-        <v>79384</v>
+        <v>91353</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,25 +1013,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>4217</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599190</v>
+        <v>599180</v>
       </c>
       <c r="R5" t="n">
-        <v>6371758</v>
+        <v>6371740</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,22 +1091,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122606153</v>
+        <v>122607355</v>
       </c>
       <c r="B6" t="n">
-        <v>8441</v>
+        <v>79384</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,25 +1115,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599208</v>
+        <v>599190</v>
       </c>
       <c r="R6" t="n">
-        <v>6371570</v>
+        <v>6371758</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,11 +1179,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gnaggångar o kläckhål</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1199,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122606663</v>
+        <v>122606661</v>
       </c>
       <c r="B7" t="n">
         <v>57494</v>
@@ -1306,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122606643</v>
+        <v>122607229</v>
       </c>
       <c r="B8" t="n">
-        <v>8441</v>
+        <v>95136</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1322,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1346,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599158</v>
+        <v>599183</v>
       </c>
       <c r="R8" t="n">
-        <v>6371711</v>
+        <v>6371769</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1382,11 +1388,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1413,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122606064</v>
+        <v>122606439</v>
       </c>
       <c r="B9" t="n">
-        <v>90964</v>
+        <v>90972</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1453,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599237</v>
+        <v>599161</v>
       </c>
       <c r="R9" t="n">
-        <v>6371535</v>
+        <v>6371656</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122607229</v>
+        <v>122607568</v>
       </c>
       <c r="B10" t="n">
-        <v>95128</v>
+        <v>57494</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,41 +1528,45 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599183</v>
+        <v>599204</v>
       </c>
       <c r="R10" t="n">
-        <v>6371769</v>
+        <v>6371770</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1617,10 +1622,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122606439</v>
+        <v>122606049</v>
       </c>
       <c r="B11" t="n">
-        <v>90964</v>
+        <v>95136</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,25 +1634,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1657,10 +1662,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599161</v>
+        <v>599234</v>
       </c>
       <c r="R11" t="n">
-        <v>6371656</v>
+        <v>6371534</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1719,10 +1724,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122606032</v>
+        <v>122611553</v>
       </c>
       <c r="B12" t="n">
-        <v>91354</v>
+        <v>57494</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,41 +1736,53 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5420</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hemängen, Hemängen, Sm</t>
+          <t>Kråkemåla, Kråkemåla, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599237</v>
+        <v>599233</v>
       </c>
       <c r="R12" t="n">
-        <v>6371545</v>
+        <v>6371743</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1792,9 +1809,19 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1821,10 +1848,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122611546</v>
+        <v>122607434</v>
       </c>
       <c r="B13" t="n">
-        <v>95128</v>
+        <v>8441</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1837,41 +1864,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kråkemåla, Kråkemåla, Sm</t>
+          <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599179</v>
+        <v>599199</v>
       </c>
       <c r="R13" t="n">
-        <v>6371843</v>
+        <v>6371748</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1898,19 +1921,14 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:30</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1919,29 +1937,28 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122607223</v>
+        <v>122606064</v>
       </c>
       <c r="B14" t="n">
-        <v>90964</v>
+        <v>90972</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1978,10 +1995,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599170</v>
+        <v>599237</v>
       </c>
       <c r="R14" t="n">
-        <v>6371778</v>
+        <v>6371535</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2028,22 +2045,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122606737</v>
+        <v>122606153</v>
       </c>
       <c r="B15" t="n">
-        <v>91345</v>
+        <v>8441</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2056,21 +2073,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4217</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2080,10 +2097,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599180</v>
+        <v>599208</v>
       </c>
       <c r="R15" t="n">
-        <v>6371740</v>
+        <v>6371570</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,6 +2135,11 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Gnaggångar o kläckhål</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2130,22 +2152,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122606049</v>
+        <v>122606306</v>
       </c>
       <c r="B16" t="n">
-        <v>95128</v>
+        <v>95136</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2182,10 +2204,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599234</v>
+        <v>599154</v>
       </c>
       <c r="R16" t="n">
-        <v>6371534</v>
+        <v>6371662</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2244,10 +2266,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122611553</v>
+        <v>122607223</v>
       </c>
       <c r="B17" t="n">
-        <v>57494</v>
+        <v>90972</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2260,49 +2282,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kråkemåla, Kråkemåla, Sm</t>
+          <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599233</v>
+        <v>599170</v>
       </c>
       <c r="R17" t="n">
-        <v>6371743</v>
+        <v>6371778</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2329,19 +2339,9 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>14:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2356,22 +2356,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122793956</v>
+        <v>122793949</v>
       </c>
       <c r="B18" t="n">
-        <v>95128</v>
+        <v>95136</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599063</v>
+        <v>599171</v>
       </c>
       <c r="R18" t="n">
-        <v>6371790</v>
+        <v>6371603</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2485,10 +2485,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122793949</v>
+        <v>122793956</v>
       </c>
       <c r="B19" t="n">
-        <v>95128</v>
+        <v>95136</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599171</v>
+        <v>599063</v>
       </c>
       <c r="R19" t="n">
-        <v>6371603</v>
+        <v>6371790</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2602,10 +2602,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122793941</v>
+        <v>122793965</v>
       </c>
       <c r="B20" t="n">
-        <v>8441</v>
+        <v>79384</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2614,32 +2614,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2647,10 +2645,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599230</v>
+        <v>599017</v>
       </c>
       <c r="R20" t="n">
-        <v>6371555</v>
+        <v>6371791</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2720,10 +2718,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122793965</v>
+        <v>122793941</v>
       </c>
       <c r="B21" t="n">
-        <v>79384</v>
+        <v>8441</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2732,30 +2730,32 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599017</v>
+        <v>599230</v>
       </c>
       <c r="R21" t="n">
-        <v>6371791</v>
+        <v>6371555</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 5162-2025 artfynd.xlsx
+++ b/artfynd/A 5162-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122606032</v>
+        <v>122606663</v>
       </c>
       <c r="B2" t="n">
-        <v>91362</v>
+        <v>57494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599237</v>
+        <v>599020</v>
       </c>
       <c r="R2" t="n">
-        <v>6371545</v>
+        <v>6371825</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Spillkråka lokläte</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122611546</v>
+        <v>122606439</v>
       </c>
       <c r="B3" t="n">
-        <v>95136</v>
+        <v>90972</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,45 +794,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kråkemåla, Kråkemåla, Sm</t>
+          <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599179</v>
+        <v>599161</v>
       </c>
       <c r="R3" t="n">
-        <v>6371843</v>
+        <v>6371656</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -854,28 +855,17 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -894,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122606643</v>
+        <v>122607568</v>
       </c>
       <c r="B4" t="n">
-        <v>8441</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,41 +896,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599158</v>
+        <v>599204</v>
       </c>
       <c r="R4" t="n">
-        <v>6371711</v>
+        <v>6371770</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -970,11 +964,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122606737</v>
+        <v>122606643</v>
       </c>
       <c r="B5" t="n">
-        <v>91353</v>
+        <v>8441</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,21 +1006,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4217</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,13 +1030,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599180</v>
+        <v>599158</v>
       </c>
       <c r="R5" t="n">
-        <v>6371740</v>
+        <v>6371711</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1077,6 +1066,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122607355</v>
+        <v>122606064</v>
       </c>
       <c r="B6" t="n">
-        <v>79384</v>
+        <v>90972</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1113,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599190</v>
+        <v>599237</v>
       </c>
       <c r="R6" t="n">
-        <v>6371758</v>
+        <v>6371535</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1199,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122606661</v>
+        <v>122611553</v>
       </c>
       <c r="B7" t="n">
         <v>57494</v>
@@ -1238,20 +1232,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hemängen, Hemängen, Sm</t>
+          <t>Kråkemåla, Kråkemåla, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599020</v>
+        <v>599233</v>
       </c>
       <c r="R7" t="n">
-        <v>6371825</v>
+        <v>6371743</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1278,14 +1284,19 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Spillkråka lokläte</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1323,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122607229</v>
+        <v>122606049</v>
       </c>
       <c r="B8" t="n">
         <v>95136</v>
@@ -1352,13 +1363,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599183</v>
+        <v>599234</v>
       </c>
       <c r="R8" t="n">
-        <v>6371769</v>
+        <v>6371534</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1402,22 +1413,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122606439</v>
+        <v>122606032</v>
       </c>
       <c r="B9" t="n">
-        <v>90972</v>
+        <v>91362</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1426,25 +1437,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1465,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599161</v>
+        <v>599237</v>
       </c>
       <c r="R9" t="n">
-        <v>6371656</v>
+        <v>6371545</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,10 +1527,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122607568</v>
+        <v>122607355</v>
       </c>
       <c r="B10" t="n">
-        <v>57494</v>
+        <v>79384</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,41 +1543,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599204</v>
+        <v>599190</v>
       </c>
       <c r="R10" t="n">
-        <v>6371770</v>
+        <v>6371758</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1610,19 +1617,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122606049</v>
+        <v>122611546</v>
       </c>
       <c r="B11" t="n">
         <v>95136</v>
@@ -1656,19 +1663,23 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hemängen, Hemängen, Sm</t>
+          <t>Kråkemåla, Kråkemåla, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599234</v>
+        <v>599179</v>
       </c>
       <c r="R11" t="n">
-        <v>6371534</v>
+        <v>6371843</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1695,17 +1706,28 @@
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1724,10 +1746,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122611553</v>
+        <v>122606153</v>
       </c>
       <c r="B12" t="n">
-        <v>57494</v>
+        <v>8441</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,53 +1758,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kråkemåla, Kråkemåla, Sm</t>
+          <t>Hemängen, Hemängen, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599233</v>
+        <v>599208</v>
       </c>
       <c r="R12" t="n">
-        <v>6371743</v>
+        <v>6371570</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1809,19 +1819,14 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:30</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Gnaggångar o kläckhål</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1848,10 +1853,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122607434</v>
+        <v>122606737</v>
       </c>
       <c r="B13" t="n">
-        <v>8441</v>
+        <v>91353</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1864,21 +1869,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>4217</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1888,13 +1893,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599199</v>
+        <v>599180</v>
       </c>
       <c r="R13" t="n">
-        <v>6371748</v>
+        <v>6371740</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1924,11 +1929,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1955,10 +1955,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122606064</v>
+        <v>122606306</v>
       </c>
       <c r="B14" t="n">
-        <v>90972</v>
+        <v>95136</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1967,25 +1967,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599237</v>
+        <v>599154</v>
       </c>
       <c r="R14" t="n">
-        <v>6371535</v>
+        <v>6371662</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2057,10 +2057,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122606153</v>
+        <v>122607223</v>
       </c>
       <c r="B15" t="n">
-        <v>8441</v>
+        <v>90972</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,25 +2069,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599208</v>
+        <v>599170</v>
       </c>
       <c r="R15" t="n">
-        <v>6371570</v>
+        <v>6371778</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2135,11 +2135,6 @@
           <t>2025-02-14</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Gnaggångar o kläckhål</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2152,19 +2147,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122606306</v>
+        <v>122607229</v>
       </c>
       <c r="B16" t="n">
         <v>95136</v>
@@ -2204,13 +2199,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599154</v>
+        <v>599183</v>
       </c>
       <c r="R16" t="n">
-        <v>6371662</v>
+        <v>6371769</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2254,22 +2249,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122607223</v>
+        <v>122607434</v>
       </c>
       <c r="B17" t="n">
-        <v>90972</v>
+        <v>8441</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2278,25 +2273,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2306,13 +2301,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599170</v>
+        <v>599199</v>
       </c>
       <c r="R17" t="n">
-        <v>6371778</v>
+        <v>6371748</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2342,6 +2337,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2368,10 +2368,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122793949</v>
+        <v>122793941</v>
       </c>
       <c r="B18" t="n">
-        <v>95136</v>
+        <v>8441</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2384,27 +2384,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2412,10 +2413,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599171</v>
+        <v>599230</v>
       </c>
       <c r="R18" t="n">
-        <v>6371603</v>
+        <v>6371555</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2718,10 +2719,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122793941</v>
+        <v>122793949</v>
       </c>
       <c r="B21" t="n">
-        <v>8441</v>
+        <v>95136</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2734,28 +2735,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599230</v>
+        <v>599171</v>
       </c>
       <c r="R21" t="n">
-        <v>6371555</v>
+        <v>6371603</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 5162-2025 artfynd.xlsx
+++ b/artfynd/A 5162-2025 artfynd.xlsx
@@ -2368,10 +2368,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122793941</v>
+        <v>122793949</v>
       </c>
       <c r="B18" t="n">
-        <v>8441</v>
+        <v>95136</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2384,28 +2384,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2413,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599230</v>
+        <v>599171</v>
       </c>
       <c r="R18" t="n">
-        <v>6371555</v>
+        <v>6371603</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2719,10 +2718,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122793949</v>
+        <v>122793941</v>
       </c>
       <c r="B21" t="n">
-        <v>95136</v>
+        <v>8441</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2735,27 +2734,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2180</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599171</v>
+        <v>599230</v>
       </c>
       <c r="R21" t="n">
-        <v>6371603</v>
+        <v>6371555</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 5162-2025 artfynd.xlsx
+++ b/artfynd/A 5162-2025 artfynd.xlsx
@@ -2368,10 +2368,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122793949</v>
+        <v>122793941</v>
       </c>
       <c r="B18" t="n">
-        <v>95136</v>
+        <v>8441</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2384,27 +2384,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2412,10 +2413,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599171</v>
+        <v>599230</v>
       </c>
       <c r="R18" t="n">
-        <v>6371603</v>
+        <v>6371555</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2718,10 +2719,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122793941</v>
+        <v>122793949</v>
       </c>
       <c r="B21" t="n">
-        <v>8441</v>
+        <v>95136</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2734,28 +2735,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599230</v>
+        <v>599171</v>
       </c>
       <c r="R21" t="n">
-        <v>6371555</v>
+        <v>6371603</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 5162-2025 artfynd.xlsx
+++ b/artfynd/A 5162-2025 artfynd.xlsx
@@ -2368,10 +2368,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122793941</v>
+        <v>122793949</v>
       </c>
       <c r="B18" t="n">
-        <v>8441</v>
+        <v>95139</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2384,28 +2384,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2413,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599230</v>
+        <v>599171</v>
       </c>
       <c r="R18" t="n">
-        <v>6371555</v>
+        <v>6371603</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2486,10 +2485,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122793956</v>
+        <v>122793965</v>
       </c>
       <c r="B19" t="n">
-        <v>95136</v>
+        <v>79387</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2498,31 +2497,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2530,10 +2528,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599063</v>
+        <v>599017</v>
       </c>
       <c r="R19" t="n">
-        <v>6371790</v>
+        <v>6371791</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2603,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122793965</v>
+        <v>122793941</v>
       </c>
       <c r="B20" t="n">
-        <v>79384</v>
+        <v>8441</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2615,30 +2613,32 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599017</v>
+        <v>599230</v>
       </c>
       <c r="R20" t="n">
-        <v>6371791</v>
+        <v>6371555</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2719,10 +2719,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122793949</v>
+        <v>122793956</v>
       </c>
       <c r="B21" t="n">
-        <v>95136</v>
+        <v>95139</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599171</v>
+        <v>599063</v>
       </c>
       <c r="R21" t="n">
-        <v>6371603</v>
+        <v>6371790</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 5162-2025 artfynd.xlsx
+++ b/artfynd/A 5162-2025 artfynd.xlsx
@@ -2371,7 +2371,7 @@
         <v>122793949</v>
       </c>
       <c r="B18" t="n">
-        <v>95139</v>
+        <v>95141</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>122793965</v>
       </c>
       <c r="B19" t="n">
-        <v>79387</v>
+        <v>79389</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2601,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122793941</v>
+        <v>122793956</v>
       </c>
       <c r="B20" t="n">
-        <v>8441</v>
+        <v>95141</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2617,28 +2617,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2646,10 +2645,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599230</v>
+        <v>599063</v>
       </c>
       <c r="R20" t="n">
-        <v>6371555</v>
+        <v>6371790</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2719,10 +2718,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122793956</v>
+        <v>122793941</v>
       </c>
       <c r="B21" t="n">
-        <v>95139</v>
+        <v>8441</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2735,27 +2734,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2180</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599063</v>
+        <v>599230</v>
       </c>
       <c r="R21" t="n">
-        <v>6371790</v>
+        <v>6371555</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 5162-2025 artfynd.xlsx
+++ b/artfynd/A 5162-2025 artfynd.xlsx
@@ -2368,10 +2368,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122793949</v>
+        <v>122793941</v>
       </c>
       <c r="B18" t="n">
-        <v>95141</v>
+        <v>8441</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2384,27 +2384,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2412,10 +2413,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599171</v>
+        <v>599230</v>
       </c>
       <c r="R18" t="n">
-        <v>6371603</v>
+        <v>6371555</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2488,7 +2489,7 @@
         <v>122793965</v>
       </c>
       <c r="B19" t="n">
-        <v>79389</v>
+        <v>79390</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2601,10 +2602,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122793956</v>
+        <v>122793949</v>
       </c>
       <c r="B20" t="n">
-        <v>95141</v>
+        <v>95147</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2645,10 +2646,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599063</v>
+        <v>599171</v>
       </c>
       <c r="R20" t="n">
-        <v>6371790</v>
+        <v>6371603</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2718,10 +2719,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122793941</v>
+        <v>122793956</v>
       </c>
       <c r="B21" t="n">
-        <v>8441</v>
+        <v>95147</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2734,28 +2735,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599230</v>
+        <v>599063</v>
       </c>
       <c r="R21" t="n">
-        <v>6371555</v>
+        <v>6371790</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
